--- a/data/trans_orig/IP19-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19-Estudios-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>54135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68648</t>
+          <t>68009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59328</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72009</t>
+          <t>72126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117746</t>
+          <t>117096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136573</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36503</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27517</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>41791</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59966</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>257410</t>
+          <t>256443</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>289056</t>
+          <t>287950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>312502</t>
+          <t>313367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>345252</t>
+          <t>345586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>580376</t>
+          <t>579178</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>624064</t>
+          <t>623432</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126341</t>
+          <t>127447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157987</t>
+          <t>158954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131739</t>
+          <t>131405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164489</t>
+          <t>163624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268324</t>
+          <t>268956</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312012</t>
+          <t>313210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113460</t>
+          <t>113232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132605</t>
+          <t>133225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106059</t>
+          <t>106785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124090</t>
+          <t>124653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226694</t>
+          <t>226495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253022</t>
+          <t>252123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41461</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>60834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>33485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52079</t>
+          <t>51353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79183</t>
+          <t>80082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105511</t>
+          <t>105710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439339</t>
+          <t>439213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>479666</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>489685</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>529933</t>
+          <t>530571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938758</t>
+          <t>938553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>994768</t>
+          <t>997004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192041</t>
+          <t>191403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232289</t>
+          <t>231240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>407536</t>
+          <t>405300</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>463546</t>
+          <t>463751</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59815</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73492</t>
+          <t>73352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49123</t>
+          <t>48310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63921</t>
+          <t>63676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114126</t>
+          <t>113685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134085</t>
+          <t>133866</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>44695</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64435</t>
+          <t>64876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>297308</t>
+          <t>299092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>330159</t>
+          <t>329795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>339441</t>
+          <t>339704</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>373195</t>
+          <t>373896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>651157</t>
+          <t>649123</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>695928</t>
+          <t>694701</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122051</t>
+          <t>122415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154902</t>
+          <t>153118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118506</t>
+          <t>117805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152260</t>
+          <t>151997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247983</t>
+          <t>249210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292754</t>
+          <t>294788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98631</t>
+          <t>97123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119165</t>
+          <t>118523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>106784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126828</t>
+          <t>126947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212259</t>
+          <t>212683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239750</t>
+          <t>240887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68181</t>
+          <t>69689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64105</t>
+          <t>64081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97928</t>
+          <t>96791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125419</t>
+          <t>124995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471952</t>
+          <t>473942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>511484</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>510910</t>
+          <t>510928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>551888</t>
+          <t>549636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>995433</t>
+          <t>993112</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1052562</t>
+          <t>1052883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>199907</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>239439</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>196871</t>
+          <t>199123</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>237849</t>
+          <t>237831</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>407588</t>
+          <t>407267</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>464717</t>
+          <t>467038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>43431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49601</t>
+          <t>49766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60773</t>
+          <t>60351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96399</t>
+          <t>97071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110614</t>
+          <t>110717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>310687</t>
+          <t>309473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>344090</t>
+          <t>341937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>330610</t>
+          <t>332884</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>366096</t>
+          <t>366443</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>651717</t>
+          <t>652308</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>697450</t>
+          <t>698612</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128200</t>
+          <t>130353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161603</t>
+          <t>162817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122639</t>
+          <t>122292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158125</t>
+          <t>155851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263575</t>
+          <t>262413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309308</t>
+          <t>308717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105855</t>
+          <t>106021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125604</t>
+          <t>126543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117431</t>
+          <t>116206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139291</t>
+          <t>137544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229251</t>
+          <t>230335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>258377</t>
+          <t>261242</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47099</t>
+          <t>46160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66848</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>49951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70064</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101820</t>
+          <t>98955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130946</t>
+          <t>129862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470050</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>510744</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>514544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>553440</t>
+          <t>555616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>993598</t>
+          <t>996012</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1054991</t>
+          <t>1053025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>192453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>233289</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>394224</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32923</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44227</t>
+          <t>43645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66533</t>
+          <t>65583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33096</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29459</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36512</t>
+          <t>35360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58114</t>
+          <t>57623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120297</t>
+          <t>119588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168829</t>
+          <t>168988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137731</t>
+          <t>140043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183102</t>
+          <t>181537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276994</t>
+          <t>273625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338684</t>
+          <t>336376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153051</t>
+          <t>153918</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>227066</t>
+          <t>237807</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172480</t>
+          <t>173560</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>218017</t>
+          <t>220236</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340264</t>
+          <t>339085</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>430010</t>
+          <t>432520</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101759</t>
+          <t>97510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143614</t>
+          <t>143593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136112</t>
+          <t>135335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190940</t>
+          <t>186816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247996</t>
+          <t>247828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316961</t>
+          <t>317651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34930</t>
+          <t>33918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53119</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>32824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53027</t>
+          <t>51541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73741</t>
+          <t>73467</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100576</t>
+          <t>99767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56643</t>
+          <t>55904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53573</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78176</t>
+          <t>77020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95143</t>
+          <t>97115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127314</t>
+          <t>128156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>47548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68884</t>
+          <t>67357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59842</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84695</t>
+          <t>83208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114027</t>
+          <t>114256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145394</t>
+          <t>145326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>183798</t>
+          <t>183500</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>237122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208229</t>
+          <t>204326</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259232</t>
+          <t>256473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410612</t>
+          <t>409931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>482949</t>
+          <t>482342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>222501</t>
+          <t>224188</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304187</t>
+          <t>311047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>253174</t>
+          <t>256510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>310574</t>
+          <t>309886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>494285</t>
+          <t>496703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>597464</t>
+          <t>596245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>212413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>268717</t>
+          <t>266762</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384559</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>459488</t>
+          <t>461143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66139</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59761</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71976</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>61460</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54135</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>68009</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54261</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>68446</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66139</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58913</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72126</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,16%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117096</t>
+          <t>117595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135921</t>
+          <t>137123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20706</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14869</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>27084</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>23,84%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>31,19%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29407</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22858</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>36732</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>22421</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>36606</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>32,36%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>40,42%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20706</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>14719</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>27932</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41791</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60616</t>
+          <t>60117</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>328914</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>310010</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>345155</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>68,96%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>64,99%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>418</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>273515</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>256443</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>287950</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>258442</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>288947</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>65,84%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>61,73%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>69,32%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>328914</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>313367</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>345586</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>579178</t>
+          <t>579072</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>623432</t>
+          <t>624386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148077</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>131836</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>166981</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>141882</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>127447</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>158954</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>126450</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>156955</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>148077</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>131405</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>163624</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268956</t>
+          <t>268002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313210</t>
+          <t>313316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>415397</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>415397</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>415397</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115597</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>106162</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>124112</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>124043</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>113232</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>133225</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>113890</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>133461</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>71,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>115597</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>106785</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>124653</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>73,1%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226495</t>
+          <t>225750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252123</t>
+          <t>252404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42541</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34026</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51976</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>32,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>50023</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>40841</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>60834</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>40605</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>60176</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>42541</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33485</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>51353</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80082</t>
+          <t>79801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105710</t>
+          <t>106455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>510650</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>490558</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>530092</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>70,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>67,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>692</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>459019</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>439213</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>479624</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>438868</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>476981</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>510650</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>490734</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>530571</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>70,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938553</t>
+          <t>942816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>997004</t>
+          <t>996644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>211324</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>191882</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>231416</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>32,05%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>221311</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>200706</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>241117</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>203349</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>241462</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>32,53%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>211324</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>191403</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>231240</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>405300</t>
+          <t>405660</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>463751</t>
+          <t>459488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>680330</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57030</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48514</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63297</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>67407</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59346</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73352</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59956</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73629</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>72,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57030</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48310</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63676</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>66,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113685</t>
+          <t>113600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133866</t>
+          <t>133720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,89%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29162</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22895</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37678</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>33,83%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>43,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24962</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19017</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33023</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>18740</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>32413</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>27,02%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29162</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22516</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>37882</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>33,83%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64876</t>
+          <t>64961</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>357182</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>340644</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>372127</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>72,64%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>69,28%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>75,68%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>315524</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>299092</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>329795</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>299362</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>331688</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>69,77%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>66,14%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>72,93%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>357182</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339704</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>373896</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>72,64%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>649123</t>
+          <t>647744</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>694701</t>
+          <t>694315</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>134519</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>119574</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>151057</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136686</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>122415</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>153118</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>120522</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>152848</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>30,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>134519</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>117805</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>151997</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,36%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249210</t>
+          <t>249596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294788</t>
+          <t>296167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>491701</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>491701</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>491701</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>491701</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>491701</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>491701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>117143</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>106409</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>126522</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>68,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>109414</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97123</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>118523</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>98853</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>119132</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>65,59%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>117143</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>106784</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>126947</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>68,56%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212683</t>
+          <t>211473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240887</t>
+          <t>239315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>53722</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44343</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>64456</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>57398</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48289</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>69689</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>47680</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>67959</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>34,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>53722</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>43918</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>64081</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96791</t>
+          <t>98363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124995</t>
+          <t>126205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170865</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170865</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170865</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170865</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170865</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>531356</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>510103</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>551571</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>70,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>492345</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>473942</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>513269</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>471770</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>512632</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>69,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>531356</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>510928</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>549636</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>993112</t>
+          <t>994824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1052883</t>
+          <t>1054238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>217403</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>197188</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>238656</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>26,34%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31,87%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>219046</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>198122</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>237449</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>198759</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>239621</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>30,79%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>217403</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>199123</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>237831</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>407267</t>
+          <t>405912</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>467038</t>
+          <t>465326</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>748759</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>748759</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>748759</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>748759</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>748759</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>748759</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56005</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49642</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60606</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48306</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43431</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52674</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42541</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52508</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,35%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56005</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49766</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60351</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97071</t>
+          <t>95905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110717</t>
+          <t>110473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12609</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8008</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18972</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11072</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15947</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6870</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16837</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18,65%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12609</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8263</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18848</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>32088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>349859</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>332795</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>365379</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>71,58%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>68,09%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>74,76%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>325923</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>309473</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>341937</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>308077</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>342681</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>69,01%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>65,53%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>72,4%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>349859</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>332884</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>366443</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>71,58%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>652308</t>
+          <t>651889</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>698612</t>
+          <t>699827</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>138876</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>123356</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>155940</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>146367</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>130353</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>162817</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>129609</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>164213</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>30,99%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>138876</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>122292</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>155851</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,42%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262413</t>
+          <t>261198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>308717</t>
+          <t>309136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>128267</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>117615</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>138781</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>68,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>116846</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>106021</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>126543</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>107224</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>126609</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,66%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>128267</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>116206</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>137544</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>68,41%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>230335</t>
+          <t>230456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261242</t>
+          <t>258737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>59228</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48714</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>69880</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>55857</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>46160</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>66682</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>46094</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>65479</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,34%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>59228</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>49951</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>71289</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>31,59%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98955</t>
+          <t>101460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129862</t>
+          <t>129741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>534131</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>512830</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>553813</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>491075</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>472836</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>511918</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>472227</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>511627</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>69,72%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>534131</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>514544</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>555616</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996012</t>
+          <t>998348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1053025</t>
+          <t>1055137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>210713</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>191031</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>232014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>213296</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>192453</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>231535</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>192744</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>232144</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>210713</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>189228</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>230300</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>396190</t>
+          <t>394078</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>453203</t>
+          <t>450867</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27881</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21230</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34556</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22604</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15220</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33490</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,35%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53513</t>
+          <t>45528</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43645</t>
+          <t>37073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65583</t>
+          <t>54014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20597</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14602</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28012</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>25172</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16469</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>33751</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>46,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>27526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47231</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>33767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57623</t>
+          <t>51924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6329</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11749</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,55%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5939</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2680</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10974</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>54806</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>54806</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>54806</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53715</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>53715</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>53715</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59940</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59940</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59940</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>113654</t>
+          <t>100345</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113654</t>
+          <t>100345</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113654</t>
+          <t>100345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>134805</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>116935</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>151354</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>149257</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>119588</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>168988</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>159640</t>
+          <t>140138</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140043</t>
+          <t>124517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181537</t>
+          <t>156806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>308897</t>
+          <t>274943</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>273625</t>
+          <t>251014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336376</t>
+          <t>300115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>190324</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>169334</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210869</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>40,37%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>35,92%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>178504</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>153918</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>237807</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>39,39%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>33,97%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>52,48%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195555</t>
+          <t>157426</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>173560</t>
+          <t>141395</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220236</t>
+          <t>176423</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>374059</t>
+          <t>347749</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>339085</t>
+          <t>323527</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>432520</t>
+          <t>377532</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>146289</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>125819</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>171945</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>125373</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>97510</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>143593</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>156972</t>
+          <t>127652</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135335</t>
+          <t>111888</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186816</t>
+          <t>144087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>282345</t>
+          <t>273942</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247828</t>
+          <t>248909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>317651</t>
+          <t>302800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>471418</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>471418</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>471418</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>453135</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>453135</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>453135</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512167</t>
+          <t>425216</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512167</t>
+          <t>425216</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512167</t>
+          <t>425216</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>965302</t>
+          <t>896634</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965302</t>
+          <t>896634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>965302</t>
+          <t>896634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35418</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27578</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45094</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21,71%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43940</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33918</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>52530</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>29,62%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,87%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>35,42%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41548</t>
+          <t>40651</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51541</t>
+          <t>48977</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>85488</t>
+          <t>76069</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73467</t>
+          <t>63122</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99767</t>
+          <t>87376</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59810</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49141</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>70984</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>46485</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>38202</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55904</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>31,34%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65215</t>
+          <t>48500</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>39242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77020</t>
+          <t>58919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>111700</t>
+          <t>108310</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97115</t>
+          <t>94696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128156</t>
+          <t>125029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67882</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>57062</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79741</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>41,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>34,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>48,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>57901</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47548</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>67357</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71501</t>
+          <t>59617</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59207</t>
+          <t>49737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83208</t>
+          <t>69705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>129402</t>
+          <t>127499</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114256</t>
+          <t>112380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145326</t>
+          <t>142541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163110</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163110</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163110</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>148326</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>148326</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>148326</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>178264</t>
+          <t>148768</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>178264</t>
+          <t>148768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>178264</t>
+          <t>148768</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>326590</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>326590</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>326590</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>198104</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>179474</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>220135</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>215801</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>183500</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>237122</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>232097</t>
+          <t>198436</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204326</t>
+          <t>179349</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>256473</t>
+          <t>218221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>447898</t>
+          <t>396540</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409931</t>
+          <t>367710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>482342</t>
+          <t>424287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>270730</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>246452</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>296043</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>250161</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>224188</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>311047</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>38,18%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>282829</t>
+          <t>227662</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256510</t>
+          <t>207187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>309886</t>
+          <t>249535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>532991</t>
+          <t>498391</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>496703</t>
+          <t>465133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>596245</t>
+          <t>534515</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>220500</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>194283</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>245630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>35,63%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>189213</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>160100</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>212413</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>235444</t>
+          <t>193425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210294</t>
+          <t>173608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>266762</t>
+          <t>213379</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>424657</t>
+          <t>413924</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384336</t>
+          <t>383023</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>461143</t>
+          <t>448051</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
